--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.8038824860306</v>
+        <v>12.15563090397997</v>
       </c>
       <c r="D2" t="n">
-        <v>23.35333774568065</v>
+        <v>3.794917383673106</v>
       </c>
       <c r="E2" t="n">
-        <v>1.476177208186876</v>
+        <v>0.239878796330367</v>
       </c>
       <c r="F2" t="n">
-        <v>24.49978909516853</v>
+        <v>3.981215727964886</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.75623690240435</v>
+        <v>12.63538849664071</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35291593601771</v>
+        <v>11.75734883960288</v>
       </c>
       <c r="E3" t="n">
-        <v>1.476177208186876</v>
+        <v>0.239878796330367</v>
       </c>
       <c r="F3" t="n">
-        <v>24.49978909516853</v>
+        <v>3.981215727964886</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
